--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M09/third/CF_M09_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M09/third/CF_M09_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.5167</v>
       </c>
       <c r="D13" t="n">
+        <v>0.6813</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9596</v>
       </c>
     </row>
@@ -755,14 +763,11 @@
           <t>The system shall automatically assign a floor or allow creating new ones.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -776,14 +781,11 @@
           <t>The plant is automatically assigned or new ones can be created</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -814,14 +816,11 @@
           <t>The system shall only allow deleting an intervention if it is not finalized.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -835,14 +834,11 @@
           <t>An intervention can only be removed if it is not completed.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M09_R34</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -873,14 +869,11 @@
           <t>The system shall allow assigning a name to each spot.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -894,14 +887,11 @@
           <t>Each spot can be assigned a name.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -932,14 +922,11 @@
           <t>The system shall prevent including assets that are not in the location or are already in an intervention.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -953,14 +940,11 @@
           <t>It should not be possible to include assets that are not in the location or that they are already in an intervention</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -991,14 +975,11 @@
           <t>The system shall allow adding all asset and asset-type attributes.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1012,14 +993,11 @@
           <t>All asset and asset type attributes can be added to the asset.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1050,14 +1028,11 @@
           <t>The system shall prevent introducing a new ID once one is already assigned.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_13</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1071,14 +1046,11 @@
           <t>A new ID cannot be introduced once assigned.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M09_R18</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1109,10 +1081,6 @@
           <t>View all assets available to the user</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1126,10 +1094,6 @@
           <t>View all the assets I have available</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,14 +1124,11 @@
           <t>The system shall prevent the deletion of a spot if it has assigned assets.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1181,14 +1142,11 @@
           <t>A spot cannot be deleted if it has assets assigned to it.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1219,14 +1177,11 @@
           <t>The system shall allow leaving the serial number blank, to be assigned during installation.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1240,14 +1195,11 @@
           <t>The serial number can be left blank, in which case it will be assigned during installation.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1278,14 +1230,11 @@
           <t>The system shall display the created spot automatically.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1299,14 +1248,11 @@
           <t>The created spot is automatically displayed.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1337,10 +1283,6 @@
           <t>Eliminate an intervention</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1354,10 +1296,6 @@
           <t>Remove an intervention</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1388,10 +1326,6 @@
           <t>Complete an intervention</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1405,10 +1339,6 @@
           <t>Perform and complete an intervention</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1439,10 +1369,6 @@
           <t>Introduce 3D map ID</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1456,10 +1382,6 @@
           <t>Introduce the ID of the 3D map</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1490,14 +1412,11 @@
           <t>The system shall only allow deleting an asset if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_10</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1511,14 +1430,11 @@
           <t>An asset can only be deleted if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1549,10 +1465,6 @@
           <t>Eliminate assets from a spot</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1566,10 +1478,6 @@
           <t>Remove assets from a spot</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1605,9 +1513,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1631,8 +1536,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1663,10 +1566,6 @@
           <t>Eliminate spots from a location</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1680,10 +1579,6 @@
           <t>Remove spots from a location</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1714,10 +1609,6 @@
           <t>View assets distributed in a location</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1731,10 +1622,6 @@
           <t>View the assets that are distributed across a location</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1770,9 +1657,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1796,8 +1680,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1833,9 +1715,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1859,8 +1738,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1896,9 +1773,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1922,8 +1796,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1954,10 +1826,6 @@
           <t>View assets distributed in a location in 3D map format</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1971,10 +1839,6 @@
           <t>View the assets that are distributed across a location in 3D map format</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2010,9 +1874,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2036,8 +1897,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2073,9 +1932,6 @@
           <t>C_09</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2099,8 +1955,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2131,10 +1985,6 @@
           <t>Modify asset information</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2148,10 +1998,6 @@
           <t>Modify asset information</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2187,9 +2033,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2213,8 +2056,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2245,10 +2086,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2262,10 +2099,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2301,9 +2134,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2327,8 +2157,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2359,10 +2187,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2376,10 +2200,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2415,9 +2235,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2441,8 +2258,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2473,10 +2288,6 @@
           <t>Create a new intervention</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2490,10 +2301,6 @@
           <t>Create a new intervention</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
